--- a/data/bytebite_visualization.xlsx
+++ b/data/bytebite_visualization.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>04-25-2025</t>
+          <t>25/4/2025</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Vegan</t>
+          <t xml:space="preserve">Vegan </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>01-14-2025</t>
+          <t>January 14, 2025</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>01-05-2025</t>
+          <t>5-Jan-2025</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -805,7 +805,7 @@
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t xml:space="preserve">Delivered </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Classic</t>
+          <t xml:space="preserve">Classic </t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>26.03.2025</t>
+          <t>Mar 26, 2025</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>3/6/2025</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>DÜSSELDORF</t>
+          <t xml:space="preserve">DÜSSELDORF </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>06-08-2025</t>
+          <t>June 8, 2025</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>26-Feb-2025</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>Feb 26, 2025</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>13.02.2025</t>
+          <t>13/2/2025</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>05-07-2025</t>
+          <t>May 7, 2025</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>03-26-2025</t>
+          <t>26-Mar-2025</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>18.02.2025</t>
+          <t>Feb 18, 2025</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>18.02.2025</t>
+          <t>18/2/2025</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>20.03.2025</t>
+          <t>March 20, 2025</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>20.03.2025</t>
+          <t>20-Mar-2025</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>Feb 2, 2025</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2/2/2025</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>May 23, 2025</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>13-Jun-2025</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>06-17-2025</t>
+          <t>Jun 17, 2025</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>15/3/2025</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>April 5, 2025</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>04.05.2025</t>
+          <t>4-May-2025</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>Feb 13, 2025</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>13/2/2025</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>May 9, 2025</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>03-11-2025</t>
+          <t>11-Mar-2025</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>Jan 27, 2025</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>6/4/2025</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>04-17-2025</t>
+          <t>April 17, 2025</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>22-Apr-2025</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>Mar 18, 2025</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>26/6/2025</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>03.06.2025</t>
+          <t>June 3, 2025</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>02-06-2025</t>
+          <t>6-Feb-2025</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>Jun 22, 2025</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>22/6/2025</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>05-27-2025</t>
+          <t>May 27, 2025</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>03-27-2025</t>
+          <t>27-Mar-2025</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>26.06.2025</t>
+          <t>Jun 26, 2025</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>04.06.2025</t>
+          <t>June 4, 2025</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>06-22-2025</t>
+          <t>22-Jun-2025</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>06-22-2025</t>
+          <t>Jun 22, 2025</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>04.04.2025</t>
+          <t>4/4/2025</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>28.06.2025</t>
+          <t>June 28, 2025</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>15-Jan-2025</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>05-06-2025</t>
+          <t>May 6, 2025</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">

--- a/data/bytebite_visualization.xlsx
+++ b/data/bytebite_visualization.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>14/5/2025</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>25/4/2025</t>
+          <t>25-Apr-2025</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>January 14, 2025</t>
+          <t>14 Jan 2025</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>5-Jan-2025</t>
+          <t>5.1.2025</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>April 23, 2025</t>
+          <t>23-4-2025</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>08/04/2025</t>
+          <t>8 Apr, 2025</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>June 10, 2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>5 May 2025</t>
+          <t>5-May-2025</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Mar 26, 2025</t>
+          <t>26 Mar 2025</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>9 Apr 2025</t>
+          <t>9.4.2025</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>3/6/2025</t>
+          <t>3-6-2025</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>February 4, 2025</t>
+          <t>4 Feb, 2025</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>15 Jan 2025</t>
+          <t>15/1/2025</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>June 8, 2025</t>
+          <t>8-Jun-2025</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>26-Feb-2025</t>
+          <t>26 Feb 2025</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Feb 26, 2025</t>
+          <t>26.2.2025</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>13/2/2025</t>
+          <t>13-2-2025</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>27 Jun, 2025</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>May 7, 2025</t>
+          <t>7/5/2025</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>28/01/2025</t>
+          <t>28-Jan-2025</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>26-Mar-2025</t>
+          <t>26 Mar 2025</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Feb 18, 2025</t>
+          <t>18.2.2025</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>18/2/2025</t>
+          <t>18-2-2025</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>March 20, 2025</t>
+          <t>20 Mar, 2025</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>20-Mar-2025</t>
+          <t>20/3/2025</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>26 Jun 2025</t>
+          <t>26-Jun-2025</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Feb 2, 2025</t>
+          <t>2 Feb 2025</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2/2/2025</t>
+          <t>2.2.2025</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>May 23, 2025</t>
+          <t>23-5-2025</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>June 12, 2025</t>
+          <t>12 Jun, 2025</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>13-Jun-2025</t>
+          <t>13/6/2025</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Jun 17, 2025</t>
+          <t>17-Jun-2025</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>15/3/2025</t>
+          <t>15 Mar 2025</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>April 5, 2025</t>
+          <t>5.4.2025</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>April 28, 2025</t>
+          <t>28-4-2025</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>4-May-2025</t>
+          <t>4 May, 2025</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/4/2025</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>23 May 2025</t>
+          <t>23-May-2025</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Feb 13, 2025</t>
+          <t>13 Feb 2025</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>13/2/2025</t>
+          <t>13.2.2025</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>20 Jan 2025</t>
+          <t>20-1-2025</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>May 9, 2025</t>
+          <t>9 May, 2025</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>22/5/2025</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>11 Mar 2025</t>
+          <t>11-Mar-2025</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>12/05/2025</t>
+          <t>12 May 2025</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>26/02/2025</t>
+          <t>26.2.2025</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>11-Mar-2025</t>
+          <t>11-3-2025</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Jan 27, 2025</t>
+          <t>27 Jan, 2025</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>April 17, 2025</t>
+          <t>17-Apr-2025</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>22-Apr-2025</t>
+          <t>22.4.2025</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Mar 18, 2025</t>
+          <t>18-3-2025</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>26/6/2025</t>
+          <t>26 Jun, 2025</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/6/2025</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>June 3, 2025</t>
+          <t>3-Jun-2025</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>6-Feb-2025</t>
+          <t>6 Feb 2025</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Jun 22, 2025</t>
+          <t>22.6.2025</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>22/6/2025</t>
+          <t>22-6-2025</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>10 Mar, 2025</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>May 27, 2025</t>
+          <t>27/5/2025</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>March 4, 2025</t>
+          <t>4.3.2025</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>22 Jan 2025</t>
+          <t>22-1-2025</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Jun 26, 2025</t>
+          <t>26 Jun, 2025</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>9/3/2025</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>9-Mar-2025</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>5 Jan 2025</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>April 13, 2025</t>
+          <t>13.4.2025</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>January 18, 2025</t>
+          <t>18-1-2025</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11 Feb, 2025</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>June 4, 2025</t>
+          <t>4/6/2025</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Jun 22, 2025</t>
+          <t>22 Jun 2025</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>April 4, 2025</t>
+          <t>4.4.2025</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>January 22, 2025</t>
+          <t>22-1-2025</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>4/4/2025</t>
+          <t>4 Apr, 2025</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>18 Feb 2025</t>
+          <t>18/2/2025</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>April 3, 2025</t>
+          <t>3-Apr-2025</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>June 28, 2025</t>
+          <t>28 Jun 2025</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>15-Jan-2025</t>
+          <t>15.1.2025</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>May 6, 2025</t>
+          <t>6-5-2025</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
